--- a/04_extract_results/ai_review_batches/batch_005.xlsx
+++ b/04_extract_results/ai_review_batches/batch_005.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,25 +446,55 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>previous_sentence</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>sentence</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>next_sentence</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai_relevant</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>relevance_level</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>sentence_type</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>rule_matched_pathways</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>matched_keywords</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ethanol_specific</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>oxygenate_related</t>
         </is>
@@ -486,19 +516,47 @@
           <t>S0601</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Moreover, recent study by Ager research framework, machine-learning accelerated theoretical et al.16 showed that different C 2+ products are generated from calculations, coupled with actionable experiments, for analyzing specificactivesites onOD-Cuvia isotopelabeling.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>However, the atomic structures of active sites in heterogeneous catalytic currentunderstandingofatom-scaleactivesitesoverOD-Cufalls systems. short of expectation, impeding the rational design of catalysts converting CO 2 to specific product, like ethylene and ethanol, Results with high selectivity.</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
+          <t>The difficulty is that available characterA realistic surface model is the prerequisite for the exact ization techniques cannot detect the complex surface features of analysis of atomic structure of active sites.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -520,19 +578,47 @@
           <t>S0602</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" t="n">
+        <v>14</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>(b) Partial current densities of different products for MoP-Im catalyst as a function of potentials.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>(c) Cathodic energy efficiency for C H OH formation (Cathodic EE ) of MoP-Im and MoP compared to state-of-the-art 2 5 C2H5OH catalytic systems.[11,12,26–33] The data shown in this figure are obtained at the maximum C H OH 2 5 formation FE of each catalyst in the literature considering no overpotential losses at the anode.</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
+          <t>(d) C H OH formation turnover frequency (TOF ) calculations for MoP and MoP-Im.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -554,19 +640,47 @@
           <t>S0603</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" t="n">
+        <v>27</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>M.; Scholten, F.; Kunze, S.; Rizo, R.; Roldan Cuenya, B.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>The Role of in Situ Generated Morphological Motifs and Cu(i) Species in C2+ Product Selectivity during CO 2 Pulsed Electroreduction.</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
+          <t>Nat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>no</t>
         </is>
